--- a/raw/info_weekly.xlsx
+++ b/raw/info_weekly.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rmanassero\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\estado-sistema-gas-rodrigo-clean\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{711328CB-55C7-49BA-9B42-5D0997D2AE63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9E658C-676D-4F62-A5A7-3288CE682A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{30F98B0E-57CC-4347-8C71-8A06F7DFB1C9}"/>
   </bookViews>
@@ -468,46 +468,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46272</v>
+        <v>46279</v>
       </c>
       <c r="C1" s="3">
-        <v>46273</v>
+        <v>46280</v>
       </c>
       <c r="D1" s="3">
-        <v>46274</v>
+        <v>46281</v>
       </c>
       <c r="E1" s="3">
-        <v>46275</v>
+        <v>46282</v>
       </c>
       <c r="F1" s="3">
-        <v>46276</v>
+        <v>46283</v>
       </c>
       <c r="G1" s="3">
-        <v>46277</v>
+        <v>46284</v>
       </c>
       <c r="H1" s="3">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="I1" s="3">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="J1" s="3">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="K1" s="3">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="L1" s="3">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="M1" s="3">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="N1" s="3">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="O1" s="3">
-        <v>46285</v>
+        <v>46292</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
@@ -536,10 +536,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="1">
-        <v>2734</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1">
-        <v>2734</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
         <v>0</v>
@@ -562,31 +562,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>107</v>
+        <v>559</v>
       </c>
       <c r="C3" s="1">
-        <v>231</v>
+        <v>403</v>
       </c>
       <c r="D3" s="1">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="E3" s="1">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="F3" s="1">
-        <v>118</v>
+        <v>150</v>
       </c>
       <c r="G3" s="1">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="H3" s="1">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="I3" s="1">
-        <v>559</v>
+        <v>139</v>
       </c>
       <c r="J3" s="1">
-        <v>403</v>
+        <v>137</v>
       </c>
       <c r="K3" s="1">
         <v>137</v>
@@ -601,7 +601,7 @@
         <v>86</v>
       </c>
       <c r="O3" s="1">
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -630,10 +630,10 @@
         <v>0</v>
       </c>
       <c r="I4" s="1">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="J4" s="1">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
         <v>0</v>
@@ -656,46 +656,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>32000</v>
+        <v>31000</v>
       </c>
       <c r="C5" s="1">
-        <v>32000</v>
+        <v>31000</v>
       </c>
       <c r="D5" s="1">
         <v>33000</v>
       </c>
       <c r="E5" s="1">
-        <v>32172</v>
+        <v>34827</v>
       </c>
       <c r="F5" s="1">
-        <v>30848</v>
+        <v>34733</v>
       </c>
       <c r="G5" s="1">
-        <v>28436</v>
+        <v>26468</v>
       </c>
       <c r="H5" s="1">
-        <v>26321</v>
+        <v>25474</v>
       </c>
       <c r="I5" s="1">
-        <v>31000</v>
+        <v>28701</v>
       </c>
       <c r="J5" s="1">
-        <v>31000</v>
+        <v>28701</v>
       </c>
       <c r="K5" s="1">
-        <v>33000</v>
+        <v>28701</v>
       </c>
       <c r="L5" s="1">
-        <v>34827</v>
+        <v>27621</v>
       </c>
       <c r="M5" s="1">
-        <v>34733</v>
+        <v>28789</v>
       </c>
       <c r="N5" s="1">
-        <v>26468</v>
+        <v>27225</v>
       </c>
       <c r="O5" s="1">
-        <v>25474</v>
+        <v>25961</v>
       </c>
     </row>
   </sheetData>

--- a/raw/info_weekly.xlsx
+++ b/raw/info_weekly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\estado-sistema-gas-rodrigo-clean\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE9E658C-676D-4F62-A5A7-3288CE682A6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341FF6E3-263D-40F0-B62C-77767B64576B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{30F98B0E-57CC-4347-8C71-8A06F7DFB1C9}"/>
   </bookViews>
@@ -460,65 +460,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39725982-5D6C-4C65-AEE6-7C0B298B6913}">
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46279</v>
+        <v>46286</v>
       </c>
       <c r="C1" s="3">
-        <v>46280</v>
+        <v>46287</v>
       </c>
       <c r="D1" s="3">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="E1" s="3">
-        <v>46282</v>
+        <v>46289</v>
       </c>
       <c r="F1" s="3">
-        <v>46283</v>
+        <v>46290</v>
       </c>
       <c r="G1" s="3">
-        <v>46284</v>
+        <v>46291</v>
       </c>
       <c r="H1" s="3">
-        <v>46285</v>
+        <v>46292</v>
       </c>
       <c r="I1" s="3">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="J1" s="3">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="K1" s="3">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="L1" s="3">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="M1" s="3">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="N1" s="3">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="O1" s="3">
-        <v>46292</v>
+        <v>46299</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <v>2734</v>
+        <v>0</v>
       </c>
       <c r="C2" s="1">
-        <v>2734</v>
+        <v>0</v>
       </c>
       <c r="D2" s="1">
         <v>0</v>
@@ -556,16 +556,19 @@
       <c r="O2" s="1">
         <v>0</v>
       </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>559</v>
+        <v>139</v>
       </c>
       <c r="C3" s="1">
-        <v>403</v>
+        <v>137</v>
       </c>
       <c r="D3" s="1">
         <v>137</v>
@@ -580,7 +583,7 @@
         <v>86</v>
       </c>
       <c r="H3" s="1">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I3" s="1">
         <v>139</v>
@@ -603,16 +606,19 @@
       <c r="O3" s="1">
         <v>43</v>
       </c>
+      <c r="P3">
+        <v>832</v>
+      </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1">
         <v>0</v>
@@ -650,52 +656,55 @@
       <c r="O4" s="1">
         <v>0</v>
       </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>31000</v>
+        <v>28701</v>
       </c>
       <c r="C5" s="1">
-        <v>31000</v>
+        <v>28701</v>
       </c>
       <c r="D5" s="1">
-        <v>33000</v>
+        <v>28701</v>
       </c>
       <c r="E5" s="1">
-        <v>34827</v>
+        <v>27621</v>
       </c>
       <c r="F5" s="1">
-        <v>34733</v>
+        <v>28789</v>
       </c>
       <c r="G5" s="1">
-        <v>26468</v>
+        <v>27225</v>
       </c>
       <c r="H5" s="1">
-        <v>25474</v>
+        <v>25961</v>
       </c>
       <c r="I5" s="1">
-        <v>28701</v>
+        <v>28836</v>
       </c>
       <c r="J5" s="1">
-        <v>28701</v>
+        <v>28541</v>
       </c>
       <c r="K5" s="1">
-        <v>28701</v>
+        <v>27930</v>
       </c>
       <c r="L5" s="1">
-        <v>27621</v>
+        <v>27116</v>
       </c>
       <c r="M5" s="1">
-        <v>28789</v>
+        <v>25726</v>
       </c>
       <c r="N5" s="1">
-        <v>27225</v>
+        <v>24444</v>
       </c>
       <c r="O5" s="1">
-        <v>25961</v>
+        <v>23871</v>
       </c>
     </row>
   </sheetData>

--- a/raw/info_weekly.xlsx
+++ b/raw/info_weekly.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\estado-sistema-gas-rodrigo-clean\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{341FF6E3-263D-40F0-B62C-77767B64576B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16ED8073-8542-44D2-B6BC-5ACA64477A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{30F98B0E-57CC-4347-8C71-8A06F7DFB1C9}"/>
   </bookViews>
@@ -468,46 +468,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="C1" s="3">
-        <v>46287</v>
+        <v>46294</v>
       </c>
       <c r="D1" s="3">
-        <v>46288</v>
+        <v>46295</v>
       </c>
       <c r="E1" s="3">
-        <v>46289</v>
+        <v>46296</v>
       </c>
       <c r="F1" s="3">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="G1" s="3">
-        <v>46291</v>
+        <v>46298</v>
       </c>
       <c r="H1" s="3">
-        <v>46292</v>
+        <v>46299</v>
       </c>
       <c r="I1" s="3">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="J1" s="3">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="K1" s="3">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="L1" s="3">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="M1" s="3">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="N1" s="3">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="O1" s="3">
-        <v>46299</v>
+        <v>46306</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
@@ -665,46 +665,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>28701</v>
+        <v>28836</v>
       </c>
       <c r="C5" s="1">
-        <v>28701</v>
+        <v>28541</v>
       </c>
       <c r="D5" s="1">
-        <v>28701</v>
+        <v>27930</v>
       </c>
       <c r="E5" s="1">
-        <v>27621</v>
+        <v>27116</v>
       </c>
       <c r="F5" s="1">
-        <v>28789</v>
+        <v>25726</v>
       </c>
       <c r="G5" s="1">
-        <v>27225</v>
+        <v>24444</v>
       </c>
       <c r="H5" s="1">
-        <v>25961</v>
+        <v>23871</v>
       </c>
       <c r="I5" s="1">
-        <v>28836</v>
+        <v>28241</v>
       </c>
       <c r="J5" s="1">
-        <v>28541</v>
+        <v>28517</v>
       </c>
       <c r="K5" s="1">
-        <v>27930</v>
+        <v>29256</v>
       </c>
       <c r="L5" s="1">
-        <v>27116</v>
+        <v>28888</v>
       </c>
       <c r="M5" s="1">
-        <v>25726</v>
+        <v>28378</v>
       </c>
       <c r="N5" s="1">
-        <v>24444</v>
+        <v>22050</v>
       </c>
       <c r="O5" s="1">
-        <v>23871</v>
+        <v>21054</v>
       </c>
     </row>
   </sheetData>

--- a/raw/info_weekly.xlsx
+++ b/raw/info_weekly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\estado-sistema-gas-rodrigo-clean\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16ED8073-8542-44D2-B6BC-5ACA64477A7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DE279B-AD32-4712-9F03-DCBE5E1854E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{30F98B0E-57CC-4347-8C71-8A06F7DFB1C9}"/>
   </bookViews>
@@ -468,46 +468,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46293</v>
+        <v>46300</v>
       </c>
       <c r="C1" s="3">
-        <v>46294</v>
+        <v>46301</v>
       </c>
       <c r="D1" s="3">
-        <v>46295</v>
+        <v>46302</v>
       </c>
       <c r="E1" s="3">
-        <v>46296</v>
+        <v>46303</v>
       </c>
       <c r="F1" s="3">
-        <v>46297</v>
+        <v>46304</v>
       </c>
       <c r="G1" s="3">
-        <v>46298</v>
+        <v>46305</v>
       </c>
       <c r="H1" s="3">
-        <v>46299</v>
+        <v>46306</v>
       </c>
       <c r="I1" s="3">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="J1" s="3">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="K1" s="3">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="L1" s="3">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="M1" s="3">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="N1" s="3">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="O1" s="3">
-        <v>46306</v>
+        <v>46313</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
@@ -665,46 +665,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>28836</v>
+        <v>28241</v>
       </c>
       <c r="C5" s="1">
-        <v>28541</v>
+        <v>28517</v>
       </c>
       <c r="D5" s="1">
-        <v>27930</v>
+        <v>29256</v>
       </c>
       <c r="E5" s="1">
-        <v>27116</v>
+        <v>28888</v>
       </c>
       <c r="F5" s="1">
-        <v>25726</v>
+        <v>28378</v>
       </c>
       <c r="G5" s="1">
-        <v>24444</v>
+        <v>22050</v>
       </c>
       <c r="H5" s="1">
-        <v>23871</v>
+        <v>21054</v>
       </c>
       <c r="I5" s="1">
-        <v>28241</v>
+        <v>22389</v>
       </c>
       <c r="J5" s="1">
-        <v>28517</v>
+        <v>26269</v>
       </c>
       <c r="K5" s="1">
-        <v>29256</v>
+        <v>27185</v>
       </c>
       <c r="L5" s="1">
-        <v>28888</v>
+        <v>28703</v>
       </c>
       <c r="M5" s="1">
-        <v>28378</v>
+        <v>28803</v>
       </c>
       <c r="N5" s="1">
-        <v>22050</v>
+        <v>24906</v>
       </c>
       <c r="O5" s="1">
-        <v>21054</v>
+        <v>21201</v>
       </c>
     </row>
   </sheetData>

--- a/raw/info_weekly.xlsx
+++ b/raw/info_weekly.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\estado-sistema-gas-rodrigo-clean\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68DE279B-AD32-4712-9F03-DCBE5E1854E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83F9667-E359-4A70-8AA3-FDCA66E81ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{30F98B0E-57CC-4347-8C71-8A06F7DFB1C9}"/>
   </bookViews>
@@ -468,46 +468,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46300</v>
+        <v>46307</v>
       </c>
       <c r="C1" s="3">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="D1" s="3">
-        <v>46302</v>
+        <v>46309</v>
       </c>
       <c r="E1" s="3">
-        <v>46303</v>
+        <v>46310</v>
       </c>
       <c r="F1" s="3">
-        <v>46304</v>
+        <v>46311</v>
       </c>
       <c r="G1" s="3">
-        <v>46305</v>
+        <v>46312</v>
       </c>
       <c r="H1" s="3">
-        <v>46306</v>
+        <v>46313</v>
       </c>
       <c r="I1" s="3">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="J1" s="3">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="K1" s="3">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="L1" s="3">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="M1" s="3">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="N1" s="3">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="O1" s="3">
-        <v>46313</v>
+        <v>46320</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
@@ -586,25 +586,25 @@
         <v>43</v>
       </c>
       <c r="I3" s="1">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="J3" s="1">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="K3" s="1">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="L3" s="1">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="M3" s="1">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="N3" s="1">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="O3" s="1">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="P3">
         <v>832</v>
@@ -665,46 +665,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>28241</v>
+        <v>22389</v>
       </c>
       <c r="C5" s="1">
-        <v>28517</v>
+        <v>26269</v>
       </c>
       <c r="D5" s="1">
-        <v>29256</v>
+        <v>27185</v>
       </c>
       <c r="E5" s="1">
-        <v>28888</v>
+        <v>28703</v>
       </c>
       <c r="F5" s="1">
-        <v>28378</v>
+        <v>28803</v>
       </c>
       <c r="G5" s="1">
-        <v>22050</v>
+        <v>24906</v>
       </c>
       <c r="H5" s="1">
-        <v>21054</v>
+        <v>21201</v>
       </c>
       <c r="I5" s="1">
-        <v>22389</v>
+        <v>29798</v>
       </c>
       <c r="J5" s="1">
-        <v>26269</v>
+        <v>27018</v>
       </c>
       <c r="K5" s="1">
-        <v>27185</v>
+        <v>26221</v>
       </c>
       <c r="L5" s="1">
-        <v>28703</v>
+        <v>26317</v>
       </c>
       <c r="M5" s="1">
-        <v>28803</v>
+        <v>27303</v>
       </c>
       <c r="N5" s="1">
-        <v>24906</v>
+        <v>24393</v>
       </c>
       <c r="O5" s="1">
-        <v>21201</v>
+        <v>23707</v>
       </c>
     </row>
   </sheetData>

--- a/raw/info_weekly.xlsx
+++ b/raw/info_weekly.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\estado-sistema-gas-rodrigo-clean\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B83F9667-E359-4A70-8AA3-FDCA66E81ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4537EA26-A0FC-48DA-AD13-ADFF47382859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{30F98B0E-57CC-4347-8C71-8A06F7DFB1C9}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{30F98B0E-57CC-4347-8C71-8A06F7DFB1C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -460,57 +460,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39725982-5D6C-4C65-AEE6-7C0B298B6913}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46307</v>
+        <v>46314</v>
       </c>
       <c r="C1" s="3">
-        <v>46308</v>
+        <v>46315</v>
       </c>
       <c r="D1" s="3">
-        <v>46309</v>
+        <v>46316</v>
       </c>
       <c r="E1" s="3">
-        <v>46310</v>
+        <v>46317</v>
       </c>
       <c r="F1" s="3">
-        <v>46311</v>
+        <v>46318</v>
       </c>
       <c r="G1" s="3">
-        <v>46312</v>
+        <v>46319</v>
       </c>
       <c r="H1" s="3">
-        <v>46313</v>
+        <v>46320</v>
       </c>
       <c r="I1" s="3">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="J1" s="3">
-        <v>46315</v>
+        <v>46322</v>
       </c>
       <c r="K1" s="3">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="L1" s="3">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="M1" s="3">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="N1" s="3">
-        <v>46319</v>
+        <v>46326</v>
       </c>
       <c r="O1" s="3">
-        <v>46320</v>
+        <v>46327</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -556,34 +556,31 @@
       <c r="O2" s="1">
         <v>0</v>
       </c>
-      <c r="P2">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="C3" s="1">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="D3" s="1">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="E3" s="1">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="F3" s="1">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="G3" s="1">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="H3" s="1">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="I3" s="1">
         <v>107</v>
@@ -606,11 +603,8 @@
       <c r="O3" s="1">
         <v>11</v>
       </c>
-      <c r="P3">
-        <v>832</v>
-      </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -656,55 +650,52 @@
       <c r="O4" s="1">
         <v>0</v>
       </c>
-      <c r="P4">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>22389</v>
+        <v>29798</v>
       </c>
       <c r="C5" s="1">
-        <v>26269</v>
+        <v>27018</v>
       </c>
       <c r="D5" s="1">
-        <v>27185</v>
+        <v>26221</v>
       </c>
       <c r="E5" s="1">
-        <v>28703</v>
+        <v>26317</v>
       </c>
       <c r="F5" s="1">
-        <v>28803</v>
+        <v>27303</v>
       </c>
       <c r="G5" s="1">
-        <v>24906</v>
+        <v>24393</v>
       </c>
       <c r="H5" s="1">
-        <v>21201</v>
+        <v>23707</v>
       </c>
       <c r="I5" s="1">
-        <v>29798</v>
+        <v>26577</v>
       </c>
       <c r="J5" s="1">
-        <v>27018</v>
+        <v>25512</v>
       </c>
       <c r="K5" s="1">
-        <v>26221</v>
+        <v>25904</v>
       </c>
       <c r="L5" s="1">
-        <v>26317</v>
+        <v>26642</v>
       </c>
       <c r="M5" s="1">
-        <v>27303</v>
+        <v>24992</v>
       </c>
       <c r="N5" s="1">
-        <v>24393</v>
+        <v>19410</v>
       </c>
       <c r="O5" s="1">
-        <v>23707</v>
+        <v>18004</v>
       </c>
     </row>
   </sheetData>

--- a/raw/info_weekly.xlsx
+++ b/raw/info_weekly.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\estado-sistema-gas-rodrigo-clean\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4537EA26-A0FC-48DA-AD13-ADFF47382859}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A289C5FE-425C-4DFA-AD53-DDAFC025AA12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{30F98B0E-57CC-4347-8C71-8A06F7DFB1C9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{30F98B0E-57CC-4347-8C71-8A06F7DFB1C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -468,46 +468,46 @@
         <v>0</v>
       </c>
       <c r="B1" s="3">
-        <v>46314</v>
+        <v>46321</v>
       </c>
       <c r="C1" s="3">
-        <v>46315</v>
+        <v>46322</v>
       </c>
       <c r="D1" s="3">
-        <v>46316</v>
+        <v>46323</v>
       </c>
       <c r="E1" s="3">
-        <v>46317</v>
+        <v>46324</v>
       </c>
       <c r="F1" s="3">
-        <v>46318</v>
+        <v>46325</v>
       </c>
       <c r="G1" s="3">
-        <v>46319</v>
+        <v>46326</v>
       </c>
       <c r="H1" s="3">
-        <v>46320</v>
+        <v>46327</v>
       </c>
       <c r="I1" s="3">
-        <v>46321</v>
+        <v>46328</v>
       </c>
       <c r="J1" s="3">
-        <v>46322</v>
+        <v>46329</v>
       </c>
       <c r="K1" s="3">
-        <v>46323</v>
+        <v>46330</v>
       </c>
       <c r="L1" s="3">
-        <v>46324</v>
+        <v>46331</v>
       </c>
       <c r="M1" s="3">
-        <v>46325</v>
+        <v>46332</v>
       </c>
       <c r="N1" s="3">
-        <v>46326</v>
+        <v>46333</v>
       </c>
       <c r="O1" s="3">
-        <v>46327</v>
+        <v>46334</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
@@ -583,25 +583,25 @@
         <v>11</v>
       </c>
       <c r="I3" s="1">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J3" s="1">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="K3" s="1">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="L3" s="1">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="M3" s="1">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="N3" s="1">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="O3" s="1">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.35">
@@ -656,46 +656,46 @@
         <v>4</v>
       </c>
       <c r="B5" s="1">
-        <v>29798</v>
+        <v>26577</v>
       </c>
       <c r="C5" s="1">
-        <v>27018</v>
+        <v>25512</v>
       </c>
       <c r="D5" s="1">
-        <v>26221</v>
+        <v>25904</v>
       </c>
       <c r="E5" s="1">
-        <v>26317</v>
+        <v>26642</v>
       </c>
       <c r="F5" s="1">
-        <v>27303</v>
+        <v>24992</v>
       </c>
       <c r="G5" s="1">
-        <v>24393</v>
+        <v>19410</v>
       </c>
       <c r="H5" s="1">
-        <v>23707</v>
+        <v>18004</v>
       </c>
       <c r="I5" s="1">
-        <v>26577</v>
+        <v>26278</v>
       </c>
       <c r="J5" s="1">
-        <v>25512</v>
+        <v>24417</v>
       </c>
       <c r="K5" s="1">
-        <v>25904</v>
+        <v>24984</v>
       </c>
       <c r="L5" s="1">
-        <v>26642</v>
+        <v>24520</v>
       </c>
       <c r="M5" s="1">
-        <v>24992</v>
+        <v>24572</v>
       </c>
       <c r="N5" s="1">
-        <v>19410</v>
+        <v>18176</v>
       </c>
       <c r="O5" s="1">
-        <v>18004</v>
+        <v>17355</v>
       </c>
     </row>
   </sheetData>
